--- a/student_performance_report.xlsx
+++ b/student_performance_report.xlsx
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>CSE</t>
         </is>
       </c>
       <c r="D20" t="n">
